--- a/sales_stores.xlsx
+++ b/sales_stores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ΤΟΣΟΥΝΙΔΗΣ ΚΩΣΤΑΣ\Desktop\Salesapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDD1E32-C640-4E7A-8C78-B78F0D3879FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C96899-B625-42DC-86EE-41208A99169E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,72 +20,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Κατάστημα</t>
   </si>
   <si>
-    <t>493-ΣΚΙΑΘΟΣ</t>
-  </si>
-  <si>
     <t>373-25ης ΜΑΡΤΙΟΥ &amp; ΕΓΝΑΤΙΑΣ (ΠΛΑΤΑΜΩΝΑΣ)</t>
   </si>
   <si>
     <t>237-ΛΕΠΤΟΚΑΡΥΑ</t>
   </si>
   <si>
-    <t>535-ΚΕΡΚΥΡΑ ΛΕΥΚΙΜΜΗ</t>
-  </si>
-  <si>
-    <t>567-ΚΕΡΚΥΡΑ ΣΙΔΑΡΙ ΚΑΡΟΥΣΑΔΕΣ ΜΑΡΚΑΤΟ</t>
-  </si>
-  <si>
-    <t>372-ΑΓ.ΝΙΚΟΛΑΟΥ-ΛΙΤΟΧΩΡΟ</t>
-  </si>
-  <si>
     <t>234-ΧΑΤΖΟΓΛΟΥ 2 – ΚΑΤΕΡΙΝΗ</t>
   </si>
   <si>
     <t>533-ΚΕΡΚΥΡΑ ΑΛΥΚΕΣ</t>
   </si>
   <si>
-    <t>486-Μ.ΑΛΕΞΑΝΔΡΟΥ 23 - ΣΙΑΤΙΣΤΑ</t>
-  </si>
-  <si>
     <t>229-ΙΩΑΝΝΙΝΩΝ 199 - ΠΡΕΒΕΖΑ</t>
   </si>
   <si>
-    <t>540-ΚΕΡΚΥΡΑ ΑΛΕΠΟΥ ΜΑΡΚΑΤΟ</t>
-  </si>
-  <si>
     <t>378-ΠΑΡΑΜΥΘΙΑ  ΘΕΣΠΡΩΤΙΑΣ</t>
   </si>
   <si>
     <t>374-ΜΑΝΙΑΚΟΙ ΚΑΣΤΟΡΙΑΣ</t>
   </si>
   <si>
-    <t>235-ΚΟΡΙΝΟΣ</t>
-  </si>
-  <si>
-    <t>531-ΚΕΡΚΥΡΑ ΑΧΑΡΑΒΗ</t>
-  </si>
-  <si>
-    <t>534-ΚΕΡΚΥΡΑ ΜΩΡΑΙΤΙΚΑ</t>
-  </si>
-  <si>
-    <t>208-ΕΛΕΥΘΕΡΙΟΣ-ΤΡΙΚΑΛΑ</t>
-  </si>
-  <si>
-    <t>355-Χλόη Καστοριάς</t>
-  </si>
-  <si>
-    <t>223-Ν.Ιωνία - ΒΟΛΟΣ</t>
-  </si>
-  <si>
     <t>204-ΚΑΡΑΪΣΚΑΚΗ 95 - ΚΑΡΔΙΤΣΑ</t>
   </si>
   <si>
     <t>Πωλήσεις</t>
+  </si>
+  <si>
+    <t>198-ΓΚΟΥΡΑΣ &amp; ΝΙΚΟΠΟΛΕΩΣ - ΙΩΑΝΝΙΝΑ</t>
+  </si>
+  <si>
+    <t>219-ΘΥΑΤΕΙΡΩΝ &amp; Βενιζέλου Ν.Ιωνία  - ΒΟΛΟΣ</t>
+  </si>
+  <si>
+    <t>381-ΚΟΡΑΗ ΙΩΑΝΝΙΝΑ</t>
+  </si>
+  <si>
+    <t>366-ΑΘ. ΔΙΑΚΟΥ 30 &amp; ΓΡΑΜΜΟΥ 59 (ΟΤ 226)</t>
+  </si>
+  <si>
+    <t>225-Γ.ΠΑΠΑΝΔΡΕΟΥ 26-28 ΙΩΑΝΝΙΝΑ</t>
+  </si>
+  <si>
+    <t>315-26ο χλμ ΕΘΝΙΚΗΣ ΟΔΟΥ ΠΡΕΒΕΖΗΣ - ΙΩΑΝΝΙΝΩΝ</t>
+  </si>
+  <si>
+    <t>345-ΡΟΥΣΒΕΛΤ 49 - ΛΑΡΙΣΑ</t>
+  </si>
+  <si>
+    <t>565-ΚΕΡΚΥΡΑ ΣΑΡΟΚΟ ΜΑΡΚΑΤΟ</t>
+  </si>
+  <si>
+    <t>302-ΠΛ.ΕΛΕΥΘΕΡΙΑΣ - KOZANH</t>
+  </si>
+  <si>
+    <t>228-ΚΑΡΥΩΤΑΚΗ 15 &amp; ΛΕΩΦ. ΕΙΡΗΝΗΣ - ΠΡΕΒΕΖΑ</t>
+  </si>
+  <si>
+    <t>215-ΑΒΕΡΩΦ ΚΑΙ ΛΑΡΙΣΗΣ</t>
   </si>
 </sst>
 </file>
@@ -470,39 +467,39 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>233</v>
+        <v>52.92</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>117</v>
+        <v>42.039999999999992</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1">
-        <v>112</v>
+        <v>37.019999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>100</v>
+        <v>35.590000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -510,124 +507,124 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>70</v>
+        <v>32.160000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1">
-        <v>68</v>
+        <v>29.32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1">
-        <v>48</v>
+        <v>28.919999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B10" s="1">
-        <v>40</v>
+        <v>25.669999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1">
-        <v>39</v>
+        <v>23.28</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1">
-        <v>36</v>
+        <v>21.850000000000005</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1">
-        <v>33</v>
+        <v>21.81</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1">
-        <v>29</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1">
-        <v>28</v>
+        <v>19.759999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>28</v>
+        <v>18.769999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>26</v>
+        <v>18.239999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>25</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>25</v>
+        <v>16.919999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>24</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B21" s="1">
         <v>10.190000000000001</v>
